--- a/25-2_Horyeong/Assets/Resources/DT_Object.xlsx
+++ b/25-2_Horyeong/Assets/Resources/DT_Object.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bcd9b5e882ad235f/문서/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\25-2_Horyeong_2\25-2_Horyeong\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{44A0667E-B3A4-4F4B-8AF3-826669F51799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D2C7596-8C8B-44B5-9A98-C42689A1F52D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2355F3E5-89A6-4D54-8791-EE055A3A9C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="20190" windowHeight="12285" xr2:uid="{868A3B22-13F7-4B89-B0F6-E552E426852D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{868A3B22-13F7-4B89-B0F6-E552E426852D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
   <si>
     <t>ID</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>String</t>
   </si>
   <si>
     <t>changeImage</t>
@@ -93,10 +90,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Ch1_Obj_06_0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>텅 비어있네.. 배고픈데.. 밖에 나가 식량을 구해야겠다..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -104,43 +97,10 @@
     <t>DT_Shelf</t>
   </si>
   <si>
-    <t>DT_2mart24_Door</t>
-  </si>
-  <si>
-    <t>DT_LargeTrashCan</t>
-  </si>
-  <si>
-    <t>DT_JerryCan</t>
-  </si>
-  <si>
-    <t>DT_EmptyJerryCan</t>
-  </si>
-  <si>
     <t>DT_Seolhan’s_Bag</t>
   </si>
   <si>
     <t>DT_Lighter</t>
-  </si>
-  <si>
-    <t>Ch1_Obj_07_0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>문이 사슬로 묶여있네.
-잘하면 열 수 있겠는데…?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>왠지 밀 수 있을 것 같아.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이걸로 불을 붙일 수 있겠어!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>텅 비어있다..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>가방의 피가 묻어있어..
@@ -152,14 +112,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Ch1_Obj_08_0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ch1_Obj_09_0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DT_V_Table</t>
   </si>
   <si>
@@ -170,6 +122,44 @@
   </si>
   <si>
     <t>통조림이 있어! 다행이다..</t>
+  </si>
+  <si>
+    <t>String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Obj_02_1</t>
+  </si>
+  <si>
+    <t>end</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Obj_02_2</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_01_1</t>
+  </si>
+  <si>
+    <t>end</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아직 마르지 않은 걸 보니…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Obj_02_3</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_03_1</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Obj_05_1</t>
   </si>
 </sst>
 </file>
@@ -555,8 +545,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED5F376-D925-4CF1-963C-ACEDF18EA817}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="9" width="20.5625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
@@ -581,76 +574,70 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="101.25" x14ac:dyDescent="0.6">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
       </c>
       <c r="I4" s="1" t="b">
         <v>0</v>
@@ -658,150 +645,183 @@
     </row>
     <row r="5" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="151.9" x14ac:dyDescent="0.6">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="G12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="50.65" x14ac:dyDescent="0.6">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="I12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A13" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="I13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.6">
       <c r="I14" s="1"/>
@@ -814,6 +834,12 @@
     </row>
     <row r="17" spans="9:9" x14ac:dyDescent="0.6">
       <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="9:9" x14ac:dyDescent="0.6">
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="9:9" x14ac:dyDescent="0.6">
+      <c r="I19" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/25-2_Horyeong/Assets/Resources/DT_Object.xlsx
+++ b/25-2_Horyeong/Assets/Resources/DT_Object.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\25-2_Horyeong_2\25-2_Horyeong\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2355F3E5-89A6-4D54-8791-EE055A3A9C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E60DF9E-3CC5-439B-94C5-BE1B30B02EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{868A3B22-13F7-4B89-B0F6-E552E426852D}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -103,19 +103,8 @@
     <t>DT_Lighter</t>
   </si>
   <si>
-    <t>가방의 피가 묻어있어..
-아직 마르지 않은 걸 보니… 근처에 누군가 있나 봐.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이건… 나중에 꽤 유용하게 쓰일 거야.</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DT_V_Table</t>
-  </si>
-  <si>
-    <t>DT_V_kitchencabinet</t>
   </si>
   <si>
     <t>이건..</t>
@@ -145,10 +134,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>아직 마르지 않은 걸 보니…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Ch1_Obj_02_3</t>
   </si>
   <si>
@@ -160,6 +145,26 @@
   </si>
   <si>
     <t>Ch1_Obj_05_1</t>
+  </si>
+  <si>
+    <t>DT_V_kitchencabinet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DT_V_Table</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가방의 피가 묻어있어..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아직 마르지 않은 걸 보니</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근처에 누군가 있나 봐..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -574,7 +579,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
@@ -605,22 +610,22 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1"/>
       <c r="F3" s="2"/>
       <c r="G3" s="1"/>
       <c r="H3" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I3" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -637,7 +642,7 @@
         <v>8</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I4" s="1" t="b">
         <v>0</v>
@@ -645,7 +650,7 @@
     </row>
     <row r="5" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>10</v>
@@ -660,15 +665,15 @@
         <v>8</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I5" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="67.5" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
@@ -683,7 +688,7 @@
         <v>8</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I6" s="1" t="b">
         <v>0</v>
@@ -691,16 +696,16 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1"/>
       <c r="F7" s="2"/>
       <c r="G7" s="1"/>
       <c r="H7" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I7" s="1" t="b">
         <v>0</v>
@@ -723,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" s="1" t="b">
         <v>0</v>
@@ -731,16 +736,16 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1"/>
       <c r="F9" s="2"/>
       <c r="G9" s="1"/>
       <c r="H9" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I9" s="1" t="b">
         <v>0</v>
@@ -757,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I10" s="1" t="b">
         <v>0</v>
@@ -771,16 +776,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1"/>
       <c r="F11" s="3"/>
       <c r="G11" s="1"/>
       <c r="H11" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I11" s="1" t="b">
         <v>0</v>
@@ -797,13 +802,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I12" s="1" t="b">
         <v>0</v>
@@ -811,13 +816,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I13" s="1" t="b">
         <v>0</v>

--- a/25-2_Horyeong/Assets/Resources/DT_Object.xlsx
+++ b/25-2_Horyeong/Assets/Resources/DT_Object.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\25-2_Horyeong_2\25-2_Horyeong\Assets\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asura\OneDrive\문서\GitHub\25-2_Horyeong_2\25-2_Horyeong\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E60DF9E-3CC5-439B-94C5-BE1B30B02EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D6AD31-4880-4A98-BCBD-8E0294548C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{868A3B22-13F7-4B89-B0F6-E552E426852D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{868A3B22-13F7-4B89-B0F6-E552E426852D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -90,10 +90,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>텅 비어있네.. 배고픈데.. 밖에 나가 식량을 구해야겠다..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DT_Shelf</t>
   </si>
   <si>
@@ -101,16 +97,6 @@
   </si>
   <si>
     <t>DT_Lighter</t>
-  </si>
-  <si>
-    <t>이건… 나중에 꽤 유용하게 쓰일 거야.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이건..</t>
-  </si>
-  <si>
-    <t>통조림이 있어! 다행이다..</t>
   </si>
   <si>
     <t>String</t>
@@ -155,16 +141,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>가방의 피가 묻어있어..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아직 마르지 않은 걸 보니</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>근처에 누군가 있나 봐..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>텅 비어있네.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밖에서 식량을 구해야겠어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가방에 피가 묻어있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아직 마르지 않은 걸 보니…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근처에 누군가 있을 것 같아.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건… 나중에 꽤 유용하게 쓸 수 있겠네.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 통조림.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운이 좋은 걸.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Obj_05_2</t>
   </si>
 </sst>
 </file>
@@ -254,9 +267,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -294,7 +307,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -400,7 +413,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -542,7 +555,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -550,13 +563,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED5F376-D925-4CF1-963C-ACEDF18EA817}">
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="9" width="20.5625" customWidth="1"/>
+    <col min="1" max="9" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -579,13 +592,13 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -596,61 +609,67 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="2" t="s">
-        <v>24</v>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
       </c>
       <c r="I3" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A5" t="s">
-        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>10</v>
@@ -659,21 +678,21 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I5" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
@@ -682,87 +701,99 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="2" t="s">
-        <v>24</v>
+      <c r="G9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" t="s">
+        <v>35</v>
       </c>
       <c r="I9" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>33</v>
+      <c r="F10" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>8</v>
@@ -774,77 +805,138 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H11" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="I11" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>14</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A13" t="s">
-        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="C13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="H13" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="I13" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.6">
+    <row r="17" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="9:9" x14ac:dyDescent="0.6">
+    <row r="18" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="9:9" x14ac:dyDescent="0.6">
+    <row r="19" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I21" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/25-2_Horyeong/Assets/Resources/DT_Object.xlsx
+++ b/25-2_Horyeong/Assets/Resources/DT_Object.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asura\OneDrive\문서\GitHub\25-2_Horyeong_2\25-2_Horyeong\Assets\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\25-2_Horyeong_2\25-2_Horyeong\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21D6AD31-4880-4A98-BCBD-8E0294548C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477412C9-305F-42A8-8CB0-EEE1CB71DF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{868A3B22-13F7-4B89-B0F6-E552E426852D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{868A3B22-13F7-4B89-B0F6-E552E426852D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="85">
   <si>
     <t>ID</t>
   </si>
@@ -126,58 +126,224 @@
     <t>Ch1_Obj_03_1</t>
   </si>
   <si>
+    <t>Ch1_Obj_05_1</t>
+  </si>
+  <si>
+    <t>DT_V_kitchencabinet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DT_V_Table</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텅 비어있네.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밖에서 식량을 구해야겠어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가방에 피가 묻어있어.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아직 마르지 않은 걸 보니…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근처에 누군가 있을 것 같아.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건… 나중에 꽤 유용하게 쓸 수 있겠네.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아, 통조림.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운이 좋은 걸.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Obj_05_2</t>
+  </si>
+  <si>
+    <t>talk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_01_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DT_Col_Moving_To_Shelf</t>
+  </si>
+  <si>
+    <t>Ch1_Col_01_1</t>
+  </si>
+  <si>
+    <t>흐으음.. 배고파..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서랍에 음식이 있었던가..</t>
+  </si>
+  <si>
+    <t>Ch1_Col_02_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_01_2</t>
+  </si>
+  <si>
+    <t>DT_Col_Jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쓰레기통이 넘어져 길을 막고 있잖아..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_02_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DT_Col_Hungry</t>
+  </si>
+  <si>
+    <t>하아 배고파..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_03_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_03_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DT_Col_Find_Villa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빌라다..! 저기서 식량을 구하자!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_04_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_04_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DT_Col_Friend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나도 동료가 있었으면..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_05_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_05_1</t>
+  </si>
+  <si>
+    <t>DT_Col_Find_Bag</t>
+  </si>
+  <si>
+    <t>DT_Col_Find_Bag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가방이다!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_06_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_06_1</t>
+  </si>
+  <si>
+    <t>DT_Col_Find_Mart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_07_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_07_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저기에 가방 주인이 있을거야!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20XX.XX.XX 강민석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키우던 고양이가 변신해버렸다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고양이는 부모님을 잡아먹었다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무섭다. 누가 도와줬으면..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고양이가 방 문을 긁는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>( 끝난건가 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Ch1_Obj_04_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ch1_Obj_05_1</t>
-  </si>
-  <si>
-    <t>DT_V_kitchencabinet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DT_V_Table</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>텅 비어있네.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>밖에서 식량을 구해야겠어.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가방에 피가 묻어있어.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아직 마르지 않은 걸 보니…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>근처에 누군가 있을 것 같아.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이건… 나중에 꽤 유용하게 쓸 수 있겠네.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이건…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아, 통조림.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>운이 좋은 걸.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ch1_Obj_05_2</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_2</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_3</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_4</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_5</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_6</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -267,9 +433,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -307,7 +473,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -413,7 +579,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -555,7 +721,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -563,13 +729,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED5F376-D925-4CF1-963C-ACEDF18EA817}">
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="9" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,7 +764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -615,13 +781,13 @@
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -638,13 +804,13 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I3" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -667,7 +833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -684,13 +850,13 @@
         <v>8</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -707,13 +873,13 @@
         <v>8</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I6" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -730,13 +896,13 @@
         <v>8</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -759,7 +925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -776,13 +942,13 @@
         <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I9" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -805,7 +971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -816,44 +982,44 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I11" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="I12" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
@@ -868,15 +1034,15 @@
         <v>8</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="I13" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>10</v>
@@ -891,18 +1057,18 @@
         <v>8</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="I14" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1" t="b">
         <v>0</v>
@@ -914,29 +1080,494 @@
         <v>8</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="I15" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I21" s="1"/>
+    <row r="16" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" t="s">
+        <v>45</v>
+      </c>
+      <c r="I23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I27" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I31" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I33" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" t="s">
+        <v>63</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+      <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I35" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.6">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/25-2_Horyeong/Assets/Resources/DT_Object.xlsx
+++ b/25-2_Horyeong/Assets/Resources/DT_Object.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\25-2_Horyeong_2\25-2_Horyeong\Assets\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b0e0bea03c81ddea/문서/GitHub/25-2_Horyeong_2/25-2_Horyeong/Assets/Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477412C9-305F-42A8-8CB0-EEE1CB71DF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{D0D88607-6112-4390-9BC5-A20FDF460B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{868A3B22-13F7-4B89-B0F6-E552E426852D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{868A3B22-13F7-4B89-B0F6-E552E426852D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="87">
   <si>
     <t>ID</t>
   </si>
@@ -194,10 +194,6 @@
     <t>Ch1_Col_01_1</t>
   </si>
   <si>
-    <t>흐으음.. 배고파..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>서랍에 음식이 있었던가..</t>
   </si>
   <si>
@@ -212,10 +208,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>쓰레기통이 넘어져 길을 막고 있잖아..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Ch1_Col_02_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -223,10 +215,6 @@
     <t>DT_Col_Hungry</t>
   </si>
   <si>
-    <t>하아 배고파..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Ch1_Col_03_0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -239,110 +227,128 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>빌라다..! 저기서 식량을 구하자!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Ch1_Col_04_0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>DT_Col_Friend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_05_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_05_1</t>
+  </si>
+  <si>
+    <t>DT_Col_Find_Bag</t>
+  </si>
+  <si>
+    <t>DT_Col_Find_Bag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_06_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_06_1</t>
+  </si>
+  <si>
+    <t>DT_Col_Find_Mart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_07_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Col_07_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20XX.XX.XX 강민석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키우던 고양이가 변신해버렸다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고양이는 부모님을 잡아먹었다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고양이가 방 문을 긁는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_1</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_2</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_3</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_4</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_5</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_6</t>
+  </si>
+  <si>
+    <t>Ch1_Obj_04_7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Ch1_Col_04_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DT_Col_Friend</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나도 동료가 있었으면..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ch1_Col_05_0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ch1_Col_05_1</t>
-  </si>
-  <si>
-    <t>DT_Col_Find_Bag</t>
-  </si>
-  <si>
-    <t>DT_Col_Find_Bag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가방이다!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ch1_Col_06_0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ch1_Col_06_1</t>
-  </si>
-  <si>
-    <t>DT_Col_Find_Mart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ch1_Col_07_0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ch1_Col_07_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>저기에 가방 주인이 있을거야!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20XX.XX.XX 강민석</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>키우던 고양이가 변신해버렸다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고양이는 부모님을 잡아먹었다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>무섭다. 누가 도와줬으면..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고양이가 방 문을 긁는다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>( 끝난건가 )</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ch1_Obj_04_1</t>
-  </si>
-  <si>
-    <t>Ch1_Obj_04_2</t>
-  </si>
-  <si>
-    <t>Ch1_Obj_04_3</t>
-  </si>
-  <si>
-    <t>Ch1_Obj_04_4</t>
-  </si>
-  <si>
-    <t>Ch1_Obj_04_5</t>
-  </si>
-  <si>
-    <t>Ch1_Obj_04_6</t>
-  </si>
-  <si>
-    <t>Ch1_Obj_04_7</t>
+  </si>
+  <si>
+    <t>Ch1_Col_04_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빌라다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저기서 식량을 구해볼까.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누가 히어로처럼 구해줬으면 좋겠다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가방이다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마트… 여기에 가방 주인이 있을까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쓰레기통이 넘어져 길을 막고 있잖아…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하아 배고파…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배고파…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>끝난 건가.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무섭다. 누가 도와줬으면…</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -433,9 +439,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -473,7 +479,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -579,7 +585,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -721,7 +727,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -729,13 +735,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED5F376-D925-4CF1-963C-ACEDF18EA817}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <dimension ref="A1:I37"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -764,7 +770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -787,7 +793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -810,7 +816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -833,7 +839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -856,7 +862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -879,7 +885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -902,7 +908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -925,7 +931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -948,7 +954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -971,7 +977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -994,9 +1000,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
@@ -1011,15 +1017,15 @@
         <v>8</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I12" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>10</v>
@@ -1034,15 +1040,15 @@
         <v>8</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I13" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>10</v>
@@ -1057,15 +1063,15 @@
         <v>8</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I14" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>10</v>
@@ -1080,15 +1086,15 @@
         <v>8</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="I15" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>10</v>
@@ -1103,15 +1109,15 @@
         <v>8</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I16" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>10</v>
@@ -1126,15 +1132,15 @@
         <v>8</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I17" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>20</v>
@@ -1155,7 +1161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -1178,7 +1184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -1201,7 +1207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1224,7 +1230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1241,13 +1247,13 @@
         <v>41</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="I22" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -1264,15 +1270,15 @@
         <v>41</v>
       </c>
       <c r="H23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I23" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>20</v>
@@ -1293,9 +1299,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>39</v>
@@ -1304,44 +1310,44 @@
         <v>0</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>48</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I25" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A26" t="s">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>50</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I26" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A27" t="s">
-        <v>53</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>39</v>
@@ -1350,22 +1356,22 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I27" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I27" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A28" t="s">
-        <v>54</v>
-      </c>
       <c r="B28" s="1" t="s">
         <v>20</v>
       </c>
@@ -1373,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>8</v>
@@ -1385,9 +1391,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>39</v>
@@ -1396,176 +1402,199 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>55</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="B32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I32" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A30" t="s">
+      <c r="B33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I30" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A31" t="s">
+      <c r="G34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I34" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" t="s">
+        <v>57</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I31" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A32" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I32" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A33" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I33" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I36" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>63</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I34" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="33.75" x14ac:dyDescent="0.6">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I35" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.6">
-      <c r="A36" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I36" s="1" t="b">
+      <c r="B37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="1" t="b">
         <v>0</v>
       </c>
     </row>
